--- a/data/credit_bond_all_2026-09-29.xlsx
+++ b/data/credit_bond_all_2026-09-29.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -977,7 +977,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X4" s="3"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>2.45%~2.55%</t>
+        </is>
+      </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1169,7 +1173,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X5" s="3"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>2.95%~3.05%</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1329,7 +1337,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1369,7 +1377,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1587,7 +1599,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X7" s="3"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -1715,7 +1731,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ7" s="3"/>
+      <c r="AZ7" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
@@ -1811,7 +1829,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X8" s="3"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -2461,7 +2483,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2681,7 +2707,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X12" s="3"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2857,7 +2887,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2897,7 +2927,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X13" s="3"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3073,7 +3107,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7200/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3113,7 +3147,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3245,7 +3283,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ14" s="3"/>
+      <c r="AZ14" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
@@ -3297,7 +3337,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/1.8000</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -3337,7 +3377,11 @@
           <t>4-</t>
         </is>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.79%~1.89%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3465,7 +3509,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ15" s="3"/>
+      <c r="AZ15" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
@@ -3521,7 +3567,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>1.7000/1.6300</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3561,7 +3607,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3686,6 +3736,226 @@
         </is>
       </c>
       <c r="AZ16" s="3"/>
+    </row>
+    <row r="17" customHeight="true" ht="18.0">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>26娄发02</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>09-29 17:00</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>283676.SH</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>1.90 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>26娄发01</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>4.58Y</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>2.0348</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>娄底市城市发展控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>B- 45.13</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>09-29 15:00</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="U17" s="3"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>湖南省-娄底市</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟用于置换发行人前期用于偿还“23娄发03”本金而使用的自有资金,及偿还到期的“23娄发04”公司债券本金。[23娄发03,23娄发04]</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>财信证券股份有限公司,国联民生证券承销保荐有限公司,光大证券股份有限公司,国泰海通证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>娄底市城市发展控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr">
+        <is>
+          <t>2031-10-08</t>
+        </is>
+      </c>
+      <c r="AK17" s="3"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AZ17" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-09-29.xlsx
+++ b/data/credit_bond_all_2026-09-29.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-29" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-30" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-29</t>
+          <t>数据来源：DM    2026-09-30</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,9 @@
       <c r="H3" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="4" t="n">
+        <v>-134.65</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -898,7 +900,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26赣产K1</t>
+          <t>26东泰投资MTN001</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -906,37 +908,41 @@
           <t>09-29 18:00</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>520511.SZ</t>
-        </is>
-      </c>
+      <c r="C4" s="3"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7.0</v>
+        <v>7.8</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 1.72</t>
         </is>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>25东泰投资MTN001</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>1.47Y</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6060</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -946,10 +952,14 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>赣州产业投资集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="P4" s="3"/>
+          <t>如东县东泰社会发展投资有限责任公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>C- 14.37</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -957,12 +967,12 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>09-29 15:00</t>
+          <t>09-29 09:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -970,43 +980,47 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>江西省-赣州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于认购科技创新领域基金份额或置换发行前十二个月用于科技创新领域基金出资的自有资金支出</t>
+          <t>发行人本期债务融资工具发行金额为7.80亿元,募集资金全部用于偿还发行人本部存量债务融资工具本金[26东泰投资SCP003]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,华福证券股份有限公司,国信证券股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1016,59 +1030,79 @@
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种一)</t>
+          <t>如东县东泰社会发展投资有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2031-09-30</t>
-        </is>
-      </c>
-      <c r="AK4" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK4" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>其它</t>
-        </is>
-      </c>
-      <c r="AP4" s="3"/>
-      <c r="AQ4" s="3"/>
-      <c r="AR4" s="3"/>
-      <c r="AS4" s="3"/>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>多元金融</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -1089,40 +1123,42 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26赣产K2</t>
+          <t>莱特转债</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
+          <t>09-29 15:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>520512.SZ</t>
+          <t>118077.SH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>7.0</v>
+        <v>5.25</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>2.30 ~ 3.30</t>
-        </is>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>-134.65</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -1142,7 +1178,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>赣州产业投资集团有限责任公司</t>
+          <t>陕西莱特光电材料股份有限公司</t>
         </is>
       </c>
       <c r="P5" s="3"/>
@@ -1153,7 +1189,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>09-29 15:00</t>
+          <t>09-29 09:30</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1163,71 +1199,71 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U5" s="3"/>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>2.95%~3.05%</t>
-        </is>
-      </c>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X5" s="3"/>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z5" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>江西省-赣州市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于认购科技创新领域基金份额或置换发行前十二个月用于科技创新领域基金出资的自有资金支出</t>
+          <t>调整后拟募集资金总额不超过52,477.98万元,扣除发行费用后的募集资金净额将用于蒲城莱特光电新材料生产研发基地建设项目生产车间1、生产车间3和生产车间4项目、蒲城莱特生产车间数智化升级改造项目</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,华福证券股份有限公司,国信证券股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种二)</t>
+          <t>2026年陕西莱特光电材料股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2036-09-30</t>
+          <t>2032-09-29</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
@@ -1243,21 +1279,33 @@
       </c>
       <c r="AN5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>其它</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP5" s="3"/>
-      <c r="AQ5" s="3"/>
-      <c r="AR5" s="3"/>
-      <c r="AS5" s="3"/>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>化工制造</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>新材料</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>新材料</t>
+        </is>
+      </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>其他电子</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1290,7 +1338,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26龙源电力SCP016</t>
+          <t>26南部新城PPN003</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1301,53 +1349,53 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>21.0</v>
+        <v>0.99</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26龙源电力SCP015</t>
+          <t>26南新06</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>178D</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.5013</t>
+          <t>1.7543</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1.5100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司</t>
+          <t>重庆市南部新城产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 43.56</t>
+          <t>C- 18.75</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1367,51 +1415,51 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>重庆市-巴南区</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券拟募集资金不超过21亿元,所募集资金拟用于置换存量有息债务及补充流动资金</t>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限0.99亿元,拟全部用于偿还债务融资工具本金[24重南新城PPN003]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
+          <t>重庆银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG6" s="3" t="inlineStr">
@@ -1421,63 +1469,63 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司2026年度第十六期超短期融资券</t>
+          <t>重庆市南部新城产业投资集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
+          <t>2029-10-08</t>
         </is>
       </c>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AM6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1505,14 +1553,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ6" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ6" s="3"/>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26东泰投资MTN001</t>
+          <t>26龙源电力SCP017</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1523,53 +1569,53 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.8</v>
+        <v>15.0</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.72</t>
+          <t>1.31 ~ 1.51</t>
         </is>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>25东泰投资MTN001</t>
+          <t>26龙源电力SCP015</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>1.47Y</t>
+          <t>178D</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.6060</t>
+          <t>1.5013</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>如东县东泰社会发展投资有限责任公司</t>
+          <t>龙源电力集团股份有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C- 16.01</t>
+          <t>B- 40.85</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1579,12 +1625,12 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>09-29 09:00</t>
+          <t>09-29 14:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1592,48 +1638,52 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额为7.80亿元,募集资金全部用于偿还发行人本部存量债务融资工具本金[26东泰投资SCP003]</t>
+          <t>发行人本期超短期融资券拟募集资金21亿元,所募集资金拟用于置换存量有息债务及补充流动资金</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
@@ -1643,7 +1693,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>如东县东泰社会发展投资有限责任公司2026年度第一期中期票据</t>
+          <t>龙源电力集团股份有限公司2026年度第十七期超短期融资券</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1653,14 +1703,10 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK7" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2027-04-28</t>
+        </is>
+      </c>
+      <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -1678,32 +1724,32 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1731,14 +1777,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ7" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ7" s="3"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26通湾01</t>
+          <t>26九龙江MTN006A</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1748,43 +1792,45 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>284165.SH</t>
+          <t>102683858.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F8" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>25通州湾PPN003</t>
+          <t>26漳九Y2</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>1.99Y</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.7461</t>
+          <t>1.6874</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1794,12 +1840,12 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>江苏通州湾投资开发有限公司</t>
+          <t>漳州市九龙江集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 24.70</t>
+          <t>B- 36.23</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1809,12 +1855,12 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>09-29 16:00</t>
+          <t>09-29 09:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1826,43 +1872,43 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z8" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>福建省-漳州市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金仅用于偿还到期的公司债券本金[23通湾03]</t>
+          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>南通沿海开发集团有限公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1872,83 +1918,87 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>江苏通州湾投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-09-30</t>
-        </is>
-      </c>
-      <c r="AK8" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL8" s="3" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>医药商业</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ8" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR8" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -1961,73 +2011,77 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ8" s="3"/>
+      <c r="AZ8" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26镇风01</t>
+          <t>26九龙江MTN006B</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>09-29 17:00</t>
+          <t>09-29 18:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>284146.SH</t>
+          <t>102683859.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>23镇风02</t>
+          <t>26漳九Y3</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>49D</t>
+          <t>4.96Y+N</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.7439</t>
+          <t>1.8295</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/1.8000</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>镇江市风景旅游发展有限责任公司</t>
+          <t>漳州市九龙江集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 18.94</t>
+          <t>B- 36.23</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2037,56 +2091,60 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>09-29 15:00</t>
+          <t>09-29 09:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X9" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>1.79%~1.89%</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z9" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>福建省-漳州市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,用于偿还到期公司债券本金[23镇风01,23镇风02]</t>
+          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>镇江旅游集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2096,83 +2154,83 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>镇江市风景旅游发展有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
+          <t>2031-09-30</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>医药商业</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ9" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR9" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>旅游综合</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2185,133 +2243,149 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ9" s="3"/>
+      <c r="AZ9" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>莱特转债</t>
+          <t>26龙源电力SCP016</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>09-29 15:00</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>118077.SH</t>
-        </is>
-      </c>
+          <t>09-29 18:00</t>
+        </is>
+      </c>
+      <c r="C10" s="3"/>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.25</v>
+        <v>15.0</v>
       </c>
       <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>1.31 ~ 1.51</t>
+        </is>
+      </c>
+      <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>26龙源电力SCP015</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>178D</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>1.5013</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>1.5100/--</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>龙源电力集团股份有限公司</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>B- 40.85</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>09-29 09:00</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>陕西莱特光电材料股份有限公司</t>
-        </is>
-      </c>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>09-29 09:30</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.01</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X10" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>调整后拟募集资金总额不超过52,477.98万元,扣除发行费用后的募集资金净额将用于蒲城莱特光电新材料生产研发基地建设项目生产车间1、生产车间3和生产车间4项目、蒲城莱特生产车间数智化升级改造项目</t>
+          <t>发行人本期超短期融资券拟募集资金不超过21亿元,所募集资金拟用于置换存量有息债务及补充流动资金</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>2026年陕西莱特光电材料股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>龙源电力集团股份有限公司2026年度第十六期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2321,56 +2395,60 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2032-09-29</t>
+          <t>2027-04-28</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>风电</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AO10" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP10" s="3"/>
-      <c r="AQ10" s="3" t="inlineStr">
-        <is>
-          <t>化工制造</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>新材料</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>其他电子</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2391,54 +2469,60 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ10" s="3"/>
+      <c r="AZ10" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26南部新城PPN003</t>
+          <t>26镇风01</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
-        </is>
-      </c>
-      <c r="C11" s="3"/>
+          <t>09-29 19:00</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>284146.SH</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.99</v>
+        <v>7.7</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26南新06</t>
+          <t>23镇风02</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>49D</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.7690</t>
+          <t>1.7299</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2448,12 +2532,12 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>重庆市南部新城产业投资集团有限公司</t>
+          <t>镇江市风景旅游发展有限责任公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 20.79</t>
+          <t>C- 18.94</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2463,7 +2547,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-29 09:00</t>
+          <t>09-29 15:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2480,39 +2564,47 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>2.22%~2.32%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z11" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>重庆市-巴南区</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限0.99亿元,拟全部用于偿还债务融资工具本金[24重南新城PPN003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,用于偿还到期公司债券本金[23镇风01,23镇风02]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司,渤海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3"/>
+          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>镇江旅游集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2522,12 +2614,12 @@
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>重庆市南部新城产业投资集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>镇江市风景旅游发展有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2537,13 +2629,13 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2029-10-08</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t/>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
@@ -2558,7 +2650,7 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
@@ -2568,22 +2660,22 @@
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>旅游综合</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2593,7 +2685,7 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
@@ -2616,53 +2708,57 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>建材YK23</t>
+          <t>26通湾01</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
+          <t>09-29 19:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>246153.SH</t>
+          <t>284165.SH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.5</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>47.52</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>建材YK12</t>
+          <t>25通州湾PPN003</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.41Y+N</t>
+          <t>1.99Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6361</t>
+          <t>1.7461</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2672,12 +2768,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司</t>
+          <t>江苏通州湾投资开发有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B 53.31</t>
+          <t>C- 24.70</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2697,43 +2793,51 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
+          <t>本期债券的募集资金仅用于偿还到期的公司债券本金[23通湾03]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>南通沿海开发集团有限公司</t>
+        </is>
+      </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -2741,7 +2845,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr">
@@ -2751,17 +2855,17 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种一)</t>
+          <t>江苏通州湾投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2029-10-08</t>
+          <t>2031-09-30</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2777,37 +2881,37 @@
       </c>
       <c r="AN12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2817,12 +2921,12 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2840,64 +2944,72 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26龙源电力SCP017</t>
+          <t>建材YK24</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
-        </is>
-      </c>
-      <c r="C13" s="3"/>
+          <t>09-29 19:00</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>246154.SH</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>21.0</v>
+        <v>7.5</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
-        </is>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>30.52</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26龙源电力SCP015</t>
+          <t>建材YK20</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>178D</t>
+          <t>3.83Y+N</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.5013</t>
+          <t>1.6234</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.5100/--</t>
+          <t>1.7500/1.6300</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司</t>
+          <t>中国建材股份有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 43.56</t>
+          <t>B 52.35</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2907,7 +3019,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-29 14:00</t>
+          <t>09-29 16:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -2917,7 +3029,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="U13" s="3"/>
@@ -2929,7 +3041,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -2937,7 +3049,11 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z13" s="3"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>北京市</t>
@@ -2945,18 +3061,18 @@
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券拟募集资金21亿元,所募集资金拟用于置换存量有息债务及补充流动资金</t>
+          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,渤海银行股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -2966,12 +3082,12 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司2026年度第十七期超短期融资券</t>
+          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -2981,25 +3097,25 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -3007,27 +3123,27 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3042,7 +3158,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3060,64 +3176,68 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26九龙江MTN006A</t>
+          <t>建材YK23(取消发行)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
-        </is>
-      </c>
-      <c r="C14" s="3"/>
+          <t>09-29 19:00</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>DY246153.SH</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>3+N</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.0</v>
+        <v>7.5</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26漳九Y2</t>
+          <t>建材YK12</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>3.41Y+N</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.6895</t>
+          <t>1.6234</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.7200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司</t>
+          <t>中国建材股份有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 36.69</t>
+          <t>B 52.35</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3127,7 +3247,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-29 09:00</t>
+          <t>09-29 16:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3137,19 +3257,19 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3164,38 +3284,38 @@
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>福建省-漳州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
+          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种一)</t>
+          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3205,29 +3325,25 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2029-10-08</t>
+        </is>
+      </c>
+      <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -3235,27 +3351,27 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3270,7 +3386,7 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3283,73 +3399,71 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ14" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ14" s="3"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26九龙江MTN006B</t>
+          <t>26赣产K1</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
-        </is>
-      </c>
-      <c r="C15" s="3"/>
+          <t>09-29 19:00</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>520511.SZ</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26漳九Y3</t>
+          <t>26财欣02</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+N</t>
+          <t>4.89Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.8282</t>
+          <t>1.8148</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.8200/1.8000</t>
+          <t>--/1.7900</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t>B- 36.69</t>
-        </is>
-      </c>
+          <t>赣州产业投资集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="P15" s="3"/>
       <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3357,7 +3471,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-29 09:00</t>
+          <t>09-29 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3374,12 +3488,12 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3387,30 +3501,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>福建省-漳州市</t>
+          <t>江西省-赣州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于认购科技创新领域基金份额或置换发行前十二个月用于科技创新领域基金出资的自有资金支出</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
+          <t>光大证券股份有限公司,华福证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3420,17 +3530,17 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种二)</t>
+          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种一)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
@@ -3441,12 +3551,12 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
@@ -3456,32 +3566,28 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP15" s="3"/>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3496,7 +3602,7 @@
       </c>
       <c r="AW15" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX15" s="3" t="inlineStr">
@@ -3509,77 +3615,71 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>建材YK24</t>
+          <t>26赣产K2</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
+          <t>09-29 19:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>246154.SH</t>
+          <t>520512.SZ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.5</v>
+        <v>7.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>建材YK20</t>
+          <t>26财欣02</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>3.83Y+N</t>
+          <t>4.89Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6471</t>
+          <t>1.8148</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.7000/1.6300</t>
+          <t>--/1.7900</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>B 53.31</t>
-        </is>
-      </c>
+          <t>赣州产业投资集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="P16" s="3"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3587,7 +3687,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>09-29 16:00</t>
+          <t>09-29 15:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
@@ -3597,19 +3697,19 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.95%~3.05%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3620,17 +3720,17 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江西省-赣州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于认购科技创新领域基金份额或置换发行前十二个月用于科技创新领域基金出资的自有资金支出</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
+          <t>光大证券股份有限公司,华福证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
@@ -3641,27 +3741,27 @@
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种二)</t>
+          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种二)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
+          <t>2036-09-30</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3672,42 +3772,38 @@
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP16" s="3"/>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3722,7 +3818,7 @@
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3745,7 +3841,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-29 17:00</t>
+          <t>09-29 18:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3767,8 +3863,12 @@
           <t>1.90 ~ 2.40</t>
         </is>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>58.52</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>2.03</t>
@@ -3786,7 +3886,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.0348</t>
+          <t>2.0350</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-29.xlsx
+++ b/data/credit_bond_all_2026-09-29.xlsx
@@ -900,49 +900,45 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26东泰投资MTN001</t>
+          <t>莱特转债</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
-        </is>
-      </c>
-      <c r="C4" s="3"/>
+          <t>09-29 15:00</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>118077.SH</t>
+        </is>
+      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>6Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7.8</v>
+        <v>5.25</v>
       </c>
       <c r="F4" s="3"/>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 1.72</t>
-        </is>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>-134.65</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>25东泰投资MTN001</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>1.47Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.6060</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -952,14 +948,10 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>如东县东泰社会发展投资有限责任公司</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>C- 14.37</t>
-        </is>
-      </c>
+          <t>陕西莱特光电材料股份有限公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3"/>
       <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -967,75 +959,71 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>09-29 09:00</t>
+          <t>09-29 09:30</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>10.0</v>
-      </c>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U4" s="3"/>
+      <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>1.61%~1.71%</t>
-        </is>
-      </c>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X4" s="3"/>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z4" s="3"/>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>陕西省-西安市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额为7.80亿元,募集资金全部用于偿还发行人本部存量债务融资工具本金[26东泰投资SCP003]</t>
+          <t>调整后拟募集资金总额不超过52,477.98万元,扣除发行费用后的募集资金净额将用于蒲城莱特光电新材料生产研发基地建设项目生产车间1、生产车间3和生产车间4项目、蒲城莱特生产车间数智化升级改造项目</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>可转换债券</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>如东县东泰社会发展投资有限责任公司2026年度第一期中期票据</t>
+          <t>2026年陕西莱特光电材料股份有限公司向不特定对象发行可转换公司债券</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1045,57 +1033,49 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2032-09-29</t>
+        </is>
+      </c>
+      <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP4" s="3"/>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>新材料</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>其他电子</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1123,158 +1103,172 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>莱特转债</t>
+          <t>26南部新城PPN003</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>09-29 15:00</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>118077.SH</t>
-        </is>
-      </c>
+          <t>09-29 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>6Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.25</v>
+        <v>0.99</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
       <c r="H5" s="4" t="n">
-        <v>0.1</v>
+        <v>1.79</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-134.65</v>
+        <v>50.74</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>26南新06</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>2.94Y</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>1.7543</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>重庆市南部新城产业投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>C- 18.75</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>09-29 09:00</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>陕西莱特光电材料股份有限公司</t>
-        </is>
-      </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>09-29 09:30</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>4.45</v>
+      </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X5" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>AA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>陕西省-西安市</t>
+          <t>重庆市-巴南区</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>调整后拟募集资金总额不超过52,477.98万元,扣除发行费用后的募集资金净额将用于蒲城莱特光电新材料生产研发基地建设项目生产车间1、生产车间3和生产车间4项目、蒲城莱特生产车间数智化升级改造项目</t>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限0.99亿元,拟全部用于偿还债务融资工具本金[24重南新城PPN003]</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>重庆银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>可转换债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>2026年陕西莱特光电材料股份有限公司向不特定对象发行可转换公司债券</t>
+          <t>重庆市南部新城产业投资集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2032-09-29</t>
+          <t>2029-10-08</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AN5" s="3" t="inlineStr">
@@ -1284,28 +1278,32 @@
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP5" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>新材料</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>其他电子</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1338,7 +1336,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26南部新城PPN003</t>
+          <t>26龙源电力SCP017</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1346,56 +1344,66 @@
           <t>09-29 18:00</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>012682368.IB</t>
+        </is>
+      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>15.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+          <t>1.31 ~ 1.51</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>15.01</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26南新06</t>
+          <t>26龙源电力SCP015</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>178D</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.7543</t>
+          <t>1.5013</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>重庆市南部新城产业投资集团有限公司</t>
+          <t>龙源电力集团股份有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C- 18.75</t>
+          <t>B- 40.85</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1405,61 +1413,65 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>09-29 09:00</t>
+          <t>09-29 14:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>重庆市-巴南区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限0.99亿元,拟全部用于偿还债务融资工具本金[24重南新城PPN003]</t>
+          <t>发行人本期超短期融资券拟募集资金21亿元,所募集资金拟用于置换存量有息债务及补充流动资金</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司,渤海银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG6" s="3" t="inlineStr">
@@ -1469,23 +1481,23 @@
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>重庆市南部新城产业投资集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>龙源电力集团股份有限公司2026年度第十七期超短期融资券</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2029-10-08</t>
+          <t>2027-04-28</t>
         </is>
       </c>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1495,37 +1507,37 @@
       </c>
       <c r="AN6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1558,7 +1570,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26龙源电力SCP017</t>
+          <t>26九龙江MTN006A</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1566,56 +1578,62 @@
           <t>09-29 18:00</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>102683858.IB</t>
+        </is>
+      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26龙源电力SCP015</t>
+          <t>26漳九Y2</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>178D</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.5013</t>
+          <t>1.6874</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.5100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司</t>
+          <t>漳州市九龙江集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 40.85</t>
+          <t>B- 36.23</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1625,12 +1643,12 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>09-29 14:00</t>
+          <t>09-29 09:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1638,20 +1656,16 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="U7" s="4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V7" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1659,31 +1673,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z7" s="3"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省-漳州市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券拟募集资金21亿元,所募集资金拟用于置换存量有息债务及补充流动资金</t>
+          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,渤海银行股份有限公司</t>
+          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
@@ -1693,7 +1711,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司2026年度第十七期超短期融资券</t>
+          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1703,10 +1721,14 @@
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
-        </is>
-      </c>
-      <c r="AK7" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK7" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL7" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -1729,27 +1751,27 @@
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>产业集团</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>医药商业</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1764,7 +1786,7 @@
       </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX7" s="3" t="inlineStr">
@@ -1777,12 +1799,14 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ7" s="3"/>
+      <c r="AZ7" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26九龙江MTN006A</t>
+          <t>26九龙江MTN006B</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1792,12 +1816,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>102683858.IB</t>
+          <t>102683859.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -1808,34 +1832,38 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+          <t>1.60 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>43.52</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26漳九Y2</t>
+          <t>26漳九Y3</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>4.96Y+N</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.6874</t>
+          <t>1.8295</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/1.8000</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
@@ -1860,7 +1888,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
@@ -1868,8 +1896,12 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="U8" s="4" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.07</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
           <t>4-</t>
@@ -1877,7 +1909,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1923,7 +1955,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种一)</t>
+          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1933,14 +1965,10 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK8" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2031-09-30</t>
+        </is>
+      </c>
+      <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
           <t>2026-10-08</t>
@@ -2018,7 +2046,7 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26九龙江MTN006B</t>
+          <t>26龙源电力SCP016</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2028,60 +2056,64 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>102683859.IB</t>
+          <t>012682367.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.58Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+          <t>1.31 ~ 1.51</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>15.01</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26漳九Y3</t>
+          <t>26龙源电力SCP015</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+N</t>
+          <t>178D</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.8295</t>
+          <t>1.5013</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.8200/1.8000</t>
+          <t>1.5100/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司</t>
+          <t>龙源电力集团股份有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>B- 36.23</t>
+          <t>B- 40.85</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2096,7 +2128,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2104,16 +2136,20 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.01</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2121,35 +2157,31 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>福建省-漳州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
+          <t>发行人本期超短期融资券拟募集资金不超过21亿元,所募集资金拟用于置换存量有息债务及补充流动资金</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
@@ -2159,7 +2191,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种二)</t>
+          <t>龙源电力集团股份有限公司2026年度第十六期超短期融资券</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2169,7 +2201,7 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-09-30</t>
+          <t>2027-04-28</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
@@ -2195,27 +2227,27 @@
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2230,7 +2262,7 @@
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2244,70 +2276,78 @@
         </is>
       </c>
       <c r="AZ9" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26龙源电力SCP016</t>
+          <t>26通湾01</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
-        </is>
-      </c>
-      <c r="C10" s="3"/>
+          <t>09-29 19:00</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>284165.SH</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.58Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.31 ~ 1.51</t>
-        </is>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>47.52</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26龙源电力SCP015</t>
+          <t>25通州湾PPN003</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>178D</t>
+          <t>1.99Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.5013</t>
+          <t>1.7461</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.5100/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司</t>
+          <t>江苏通州湾投资开发有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 40.85</t>
+          <t>C- 24.70</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2317,7 +2357,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>09-29 09:00</t>
+          <t>09-29 16:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2330,78 +2370,82 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="U10" s="4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V10" s="4" t="n">
-        <v>1.01</v>
-      </c>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本期超短期融资券拟募集资金不超过21亿元,所募集资金拟用于置换存量有息债务及补充流动资金</t>
+          <t>本期债券的募集资金仅用于偿还到期的公司债券本金[23通湾03]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD10" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>南通沿海开发集团有限公司</t>
+        </is>
+      </c>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>龙源电力集团股份有限公司2026年度第十六期超短期融资券</t>
+          <t>江苏通州湾投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
+          <t>2031-09-30</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM10" s="3" t="inlineStr">
@@ -2416,32 +2460,32 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2451,7 +2495,7 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW10" s="3" t="inlineStr">
@@ -2469,14 +2513,12 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ10" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ10" s="3"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26镇风01</t>
+          <t>建材YK24</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2486,58 +2528,62 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>284146.SH</t>
+          <t>246154.SH</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>30.52</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>23镇风02</t>
+          <t>建材YK20</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>49D</t>
+          <t>3.83Y+N</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.7299</t>
+          <t>1.6234</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.6300</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>镇江市风景旅游发展有限责任公司</t>
+          <t>中国建材股份有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 18.94</t>
+          <t>B 52.35</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2547,7 +2593,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-29 15:00</t>
+          <t>09-29 16:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2560,21 +2606,23 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>1.67</v>
+      </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>2.22%~2.32%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -2584,24 +2632,20 @@
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,用于偿还到期公司债券本金[23镇风01,23镇风02]</t>
+          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>镇江旅游集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -2609,7 +2653,7 @@
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2619,12 +2663,12 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>镇江市风景旅游发展有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
@@ -2650,32 +2694,32 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>旅游综合</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2685,12 +2729,12 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -2708,7 +2752,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26通湾01</t>
+          <t>建材YK23(取消发行)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2718,47 +2762,43 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>284165.SH</t>
+          <t>DY246153.SH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.0</v>
+        <v>7.5</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>47.52</v>
-      </c>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>25通州湾PPN003</t>
+          <t>建材YK12</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>1.99Y</t>
+          <t>3.41Y+N</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.7461</t>
+          <t>1.6234</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2768,12 +2808,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>江苏通州湾投资开发有限公司</t>
+          <t>中国建材股份有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 24.70</t>
+          <t>B 52.35</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2793,24 +2833,24 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -2820,24 +2860,20 @@
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金仅用于偿还到期的公司债券本金[23通湾03]</t>
+          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>南通沿海开发集团有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -2845,7 +2881,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr">
@@ -2855,17 +2891,17 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>江苏通州湾投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-09-30</t>
+          <t>2029-10-08</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2881,37 +2917,37 @@
       </c>
       <c r="AN12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2921,12 +2957,12 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2944,72 +2980,72 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>建材YK24</t>
+          <t>26娄发02</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>09-29 19:00</t>
+          <t>09-29 18:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>246154.SH</t>
+          <t>283676.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.90 ~ 2.40</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>30.52</v>
+        <v>58.52</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>建材YK20</t>
+          <t>26娄发01</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>3.83Y+N</t>
+          <t>4.58Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6234</t>
+          <t>2.0350</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.7500/1.6300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司</t>
+          <t>娄底市城市发展控股集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B 52.35</t>
+          <t>B- 45.13</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3019,7 +3055,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-29 16:00</t>
+          <t>09-29 15:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3036,37 +3072,29 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t>1.71%~1.81%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X13" s="3"/>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>湖南省-娄底市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于置换发行人前期用于偿还“23娄发03”本金而使用的自有资金,及偿还到期的“23娄发04”公司债券本金。[23娄发03,23娄发04]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
+          <t>财信证券股份有限公司,国联民生证券承销保荐有限公司,光大证券股份有限公司,国泰海通证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3077,7 +3105,7 @@
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
@@ -3087,12 +3115,12 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种二)</t>
+          <t>娄底市城市发展控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
@@ -3118,32 +3146,32 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3158,7 +3186,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3176,7 +3204,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>建材YK23(取消发行)</t>
+          <t>26赣产K1</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3186,90 +3214,90 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>DY246153.SH</t>
+          <t>520511.SZ</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.5</v>
+        <v>7.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>64.52</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>26财欣02</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>4.89Y</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>1.8148</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>赣州产业投资集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>09-29 15:00</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>建材YK12</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>3.41Y+N</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>1.6234</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>中国建材股份有限公司</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>B 52.35</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>09-29 16:00</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>2.45%~2.55%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3277,24 +3305,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江西省-赣州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于认购科技创新领域基金份额或置换发行前十二个月用于科技创新领域基金出资的自有资金支出</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
+          <t>光大证券股份有限公司,华福证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3305,27 +3329,27 @@
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种一)(取消发行)</t>
+          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种一)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2029-10-08</t>
+          <t>2031-09-30</t>
         </is>
       </c>
       <c r="AK14" s="3"/>
@@ -3336,42 +3360,38 @@
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP14" s="3"/>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3386,7 +3406,7 @@
       </c>
       <c r="AW14" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX14" s="3" t="inlineStr">
@@ -3404,7 +3424,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26赣产K1</t>
+          <t>26赣产K2</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3414,12 +3434,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>520511.SZ</t>
+          <t>520512.SZ</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -3428,14 +3448,18 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+          <t>2.30 ~ 3.30</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>91.3</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -3455,7 +3479,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/1.7900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -3493,7 +3517,7 @@
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>2.45%~2.55%</t>
+          <t>2.95%~3.05%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3535,7 +3559,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种一)</t>
+          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种二)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3545,7 +3569,7 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-30</t>
+          <t>2036-09-30</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
@@ -3620,7 +3644,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26赣产K2</t>
+          <t>26镇风01</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3630,56 +3654,64 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>520512.SZ</t>
+          <t>284146.SH</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.0</v>
+        <v>7.7</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
-        </is>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>63.52</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26财欣02</t>
+          <t>23镇风02</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.89Y</t>
+          <t>49D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.8148</t>
+          <t>1.7299</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/1.7900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>赣州产业投资集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="P16" s="3"/>
+          <t>镇江市风景旅游发展有限责任公司</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>C- 18.94</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3697,43 +3729,51 @@
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.95%~3.05%</t>
+          <t>2.22%~2.32%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江西省-赣州市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于认购科技创新领域基金份额或置换发行前十二个月用于科技创新领域基金出资的自有资金支出</t>
+          <t>本期公司债券募集资金扣除发行费用后,用于偿还到期公司债券本金[23镇风01,23镇风02]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,华福证券股份有限公司,国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3"/>
+          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>镇江旅游集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3746,12 +3786,12 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种二)</t>
+          <t>镇江市风景旅游发展有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3761,7 +3801,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2036-09-30</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3772,38 +3812,42 @@
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP16" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>旅游综合</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3813,7 +3857,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3836,7 +3880,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26娄发02</t>
+          <t>26东泰投资MTN001</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3846,47 +3890,49 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>283676.SH</t>
+          <t>102683860.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>7.8</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>7.8</v>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.40</t>
+          <t>1.50 ~ 1.72</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>58.52</v>
+        <v>43.74</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26娄发01</t>
+          <t>25东泰投资MTN001</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.58Y</t>
+          <t>1.47Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.0350</t>
+          <t>1.6060</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3896,12 +3942,12 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>娄底市城市发展控股集团有限公司</t>
+          <t>如东县东泰社会发展投资有限责任公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 45.13</t>
+          <t>C- 14.37</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3911,27 +3957,35 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-29 15:00</t>
+          <t>09-29 09:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>1.359</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X17" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3940,23 +3994,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>湖南省-娄底市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于置换发行人前期用于偿还“23娄发03”本金而使用的自有资金,及偿还到期的“23娄发04”公司债券本金。[23娄发03,23娄发04]</t>
+          <t>发行人本期债务融资工具发行金额为7.80亿元,募集资金全部用于偿还发行人本部存量债务融资工具本金[26东泰投资SCP003]</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司,国联民生证券承销保荐有限公司,光大证券股份有限公司,国泰海通证券股份有限公司,平安证券股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -3966,75 +4020,79 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>娄底市城市发展控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>如东县东泰社会发展投资有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AO17" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ17" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4055,7 +4113,9 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-09-29.xlsx
+++ b/data/credit_bond_all_2026-09-29.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-30" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-01" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-30</t>
+          <t>数据来源：DM    2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C- 18.75</t>
+          <t>C- 16.38</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 40.85</t>
+          <t>B- 37.13</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1570,7 +1570,7 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26九龙江MTN006A</t>
+          <t>26东泰投资MTN001</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1580,45 +1580,49 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>102683858.IB</t>
+          <t>102683860.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.0</v>
+        <v>7.8</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4.0</v>
+        <v>7.8</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+          <t>1.50 ~ 1.72</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>43.74</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26漳九Y2</t>
+          <t>25东泰投资MTN001</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>1.47Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.6874</t>
+          <t>1.6060</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1628,12 +1632,12 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司</t>
+          <t>如东县东泰社会发展投资有限责任公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 36.23</t>
+          <t>C- 12.93</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1648,7 +1652,7 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1656,41 +1660,41 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>1.359</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>福建省-漳州市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
+          <t>发行人本期债务融资工具发行金额为7.80亿元,募集资金全部用于偿还发行人本部存量债务融资工具本金[26东泰投资SCP003]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
@@ -1711,7 +1715,7 @@
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种一)</t>
+          <t>如东县东泰社会发展投资有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
@@ -1746,12 +1750,12 @@
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
@@ -1761,17 +1765,17 @@
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1786,7 +1790,7 @@
       </c>
       <c r="AW7" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX7" s="3" t="inlineStr">
@@ -1800,80 +1804,74 @@
         </is>
       </c>
       <c r="AZ7" s="4" t="n">
-        <v>0.01</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26九龙江MTN006B</t>
+          <t>建材YK23(取消发行)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
+          <t>09-29 19:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>102683859.IB</t>
+          <t>DY246153.SH</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>7.5</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>43.52</v>
-      </c>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26漳九Y3</t>
+          <t>建材YK12</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>4.96Y+N</t>
+          <t>3.41Y+N</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.8295</t>
+          <t>1.6234</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.8200/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司</t>
+          <t>中国建材股份有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B- 36.23</t>
+          <t>B- 49.48</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1883,33 +1881,29 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>09-29 09:00</t>
+          <t>09-29 16:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>1.07</v>
-      </c>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1924,38 +1918,38 @@
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>福建省-漳州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
+          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
+          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种二)</t>
+          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1965,25 +1959,25 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-09-30</t>
+          <t>2029-10-08</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="AM8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -1991,27 +1985,27 @@
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>产业集团</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2026,7 +2020,7 @@
       </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -2039,9 +2033,7 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ8" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ8" s="3"/>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
@@ -2113,7 +2105,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>B- 40.85</t>
+          <t>B- 37.13</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2282,72 +2274,74 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26通湾01</t>
+          <t>26九龙江MTN006</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>09-29 19:00</t>
+          <t>09-29 18:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>284165.SH</t>
+          <t>102683859.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>47.52</v>
+        <v>43.52</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>25通州湾PPN003</t>
+          <t>26漳九Y3</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>1.99Y</t>
+          <t>4.96Y+N</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.7461</t>
+          <t>1.8295</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/1.8000</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>江苏通州湾投资开发有限公司</t>
+          <t>漳州市九龙江集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 24.70</t>
+          <t>C+ 33.88</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2357,12 +2351,12 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>09-29 16:00</t>
+          <t>09-29 09:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2370,21 +2364,25 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.07</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
@@ -2394,27 +2392,23 @@
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>福建省-漳州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金仅用于偿还到期的公司债券本金[23通湾03]</t>
+          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>南通沿海开发集团有限公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
@@ -2424,17 +2418,17 @@
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>江苏通州湾投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>漳州市九龙江集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="inlineStr">
@@ -2445,62 +2439,62 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>医药商业</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AO10" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ10" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX10" s="3" t="inlineStr">
@@ -2513,12 +2507,14 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ10" s="3"/>
+      <c r="AZ10" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>建材YK24</t>
+          <t>26通湾01</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2528,124 +2524,130 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>246154.SH</t>
+          <t>284165.SH</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F11" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>30.52</v>
+        <v>47.52</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>25通州湾PPN003</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>1.99Y</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>1.7461</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>江苏通州湾投资开发有限公司</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>C- 20.62</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>09-29 16:00</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>建材YK20</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>3.83Y+N</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>1.6234</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>1.7500/1.6300</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>中国建材股份有限公司</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t>B 52.35</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t>09-29 16:00</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1.67</v>
+        <v>3.98</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行等相关费用后,拟用于生产性支出,包括但不限于偿还有息债务、补充流动资金、项目建设及运营等符合法律法规要求的用途</t>
+          <t>本期债券的募集资金仅用于偿还到期的公司债券本金[23通湾03]</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国泰海通证券股份有限公司,申万宏源证券有限公司,中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3"/>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>南通沿海开发集团有限公司</t>
+        </is>
+      </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -2653,7 +2655,7 @@
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2663,17 +2665,17 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种二)</t>
+          <t>江苏通州湾投资开发有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
+          <t>2031-09-30</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2689,37 +2691,37 @@
       </c>
       <c r="AN11" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2729,12 +2731,12 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX11" s="3" t="inlineStr">
@@ -2752,7 +2754,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>建材YK23(取消发行)</t>
+          <t>建材YK24</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2762,12 +2764,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>DY246153.SH</t>
+          <t>246154.SH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -2776,11 +2778,15 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>30.52</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -2788,12 +2794,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>建材YK12</t>
+          <t>建材YK20</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.41Y+N</t>
+          <t>3.83Y+N</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -2803,7 +2809,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7500/1.6300</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2813,7 +2819,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B 52.35</t>
+          <t>B- 49.48</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2836,7 +2842,9 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="U12" s="3"/>
+      <c r="U12" s="4" t="n">
+        <v>1.67</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
@@ -2845,7 +2853,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.73%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2891,7 +2899,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种一)(取消发行)</t>
+          <t>中国建材股份有限公司2026年面向专业投资者公开发行科技创新可续期公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2901,7 +2909,7 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2029-10-08</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2962,7 +2970,7 @@
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -3045,7 +3053,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 45.13</t>
+          <t>B- 45.79</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3225,7 +3233,9 @@
       <c r="E14" s="4" t="n">
         <v>7.0</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
           <t>1.70 ~ 2.70</t>
@@ -3259,7 +3269,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7900</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3267,7 +3277,11 @@
           <t>赣州产业投资集团有限责任公司</t>
         </is>
       </c>
-      <c r="P14" s="3"/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>E 0.00</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3288,7 +3302,9 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>2.2</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
@@ -3424,7 +3440,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26赣产K2</t>
+          <t>26镇风01</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3434,47 +3450,47 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>520512.SZ</t>
+          <t>284146.SH</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>7.0</v>
+        <v>7.7</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.58</v>
+        <v>2.03</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>91.3</v>
+        <v>63.52</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26财欣02</t>
+          <t>23镇风02</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.89Y</t>
+          <t>49D</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.8148</t>
+          <t>1.7299</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3484,10 +3500,14 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>赣州产业投资集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="P15" s="3"/>
+          <t>镇江市风景旅游发展有限责任公司</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>C- 18.94</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3505,43 +3525,51 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>2.95%~3.05%</t>
+          <t>2.22%~2.32%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>江西省-赣州市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于认购科技创新领域基金份额或置换发行前十二个月用于科技创新领域基金出资的自有资金支出</t>
+          <t>本期公司债券募集资金扣除发行费用后,用于偿还到期公司债券本金[23镇风01,23镇风02]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,华福证券股份有限公司,国信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3"/>
+          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>镇江旅游集团有限责任公司</t>
+        </is>
+      </c>
       <c r="AE15" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3554,12 +3582,12 @@
       </c>
       <c r="AG15" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种二)</t>
+          <t>镇江市风景旅游发展有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3569,7 +3597,7 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2036-09-30</t>
+          <t>2031-10-08</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
@@ -3580,38 +3608,42 @@
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP15" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>旅游综合</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3621,7 +3653,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
@@ -3644,57 +3676,53 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26镇风01</t>
+          <t>26九龙江MTN006A(取消发行)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-29 19:00</t>
+          <t>09-29 18:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>284146.SH</t>
+          <t>DY102683858.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>7.7</v>
+        <v>4.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>63.52</v>
-      </c>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>23镇风02</t>
+          <t>26漳九Y2</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>49D</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7299</t>
+          <t>1.6874</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3704,12 +3732,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>镇江市风景旅游发展有限责任公司</t>
+          <t>漳州市九龙江集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 18.94</t>
+          <t>C+ 33.88</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3719,34 +3747,34 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>09-29 15:00</t>
+          <t>09-29 09:00</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>2.22%~2.32%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -3756,27 +3784,23 @@
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>福建省-漳州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,用于偿还到期公司债券本金[23镇风01,23镇风02]</t>
+          <t>本期中期票据发行金额8亿元,募集资金拟用于偿还发行人集团本部到期的债务融资工具[26九龙江CP001,26九龙江CP002]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>镇江旅游集团有限责任公司</t>
-        </is>
-      </c>
+          <t>中信银行股份有限公司,华泰联合证券有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3786,83 +3810,87 @@
       </c>
       <c r="AG16" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>镇江市风景旅游发展有限责任公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>漳州市九龙江集团有限公司2026年度第六期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-10-08</t>
-        </is>
-      </c>
-      <c r="AK16" s="3"/>
+          <t>2029-09-30</t>
+        </is>
+      </c>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>休8</t>
+        </is>
+      </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>产业集团</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>医药商业</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="AO16" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ16" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR16" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS16" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT16" s="3" t="inlineStr">
-        <is>
-          <t>旅游综合</t>
-        </is>
-      </c>
-      <c r="AU16" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX16" s="3" t="inlineStr">
@@ -3875,79 +3903,81 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26东泰投资MTN001</t>
+          <t>26赣产K2</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-29 18:00</t>
+          <t>09-29 19:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683860.IB</t>
+          <t>520512.SZ</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>7.8</v>
+        <v>7.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7.8</v>
+        <v>6.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.72</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>43.74</v>
+        <v>91.3</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25东泰投资MTN001</t>
+          <t>26财欣02</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>1.47Y</t>
+          <t>4.89Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6060</t>
+          <t>1.8148</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7900</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>如东县东泰社会发展投资有限责任公司</t>
+          <t>赣州产业投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C- 14.37</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3957,12 +3987,12 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-29 09:00</t>
+          <t>09-29 15:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -3971,46 +4001,44 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>1.359</v>
-      </c>
-      <c r="V17" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>2.32</v>
+      </c>
+      <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>2.95%~3.05%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>江西省-赣州市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具发行金额为7.80亿元,募集资金全部用于偿还发行人本部存量债务融资工具本金[26东泰投资SCP003]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于认购科技创新领域基金份额或置换发行前十二个月用于科技创新领域基金出资的自有资金支出</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>光大证券股份有限公司,华福证券股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4020,37 +4048,33 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>如东县东泰社会发展投资有限责任公司2026年度第一期中期票据</t>
+          <t>赣州产业投资集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(品种二)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-30</t>
-        </is>
-      </c>
-      <c r="AK17" s="3" t="inlineStr">
-        <is>
-          <t>休8</t>
-        </is>
-      </c>
+          <t>2036-09-30</t>
+        </is>
+      </c>
+      <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4060,32 +4084,28 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP17" s="3"/>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4113,9 +4133,7 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AZ17" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ17" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-09-29.xlsx
+++ b/data/credit_bond_all_2026-09-29.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-01" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-02" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-01</t>
+          <t>数据来源：DM    2026-10-02</t>
         </is>
       </c>
     </row>

--- a/data/credit_bond_all_2026-09-29.xlsx
+++ b/data/credit_bond_all_2026-09-29.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-10-02" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-10-05" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-10-02</t>
+          <t>数据来源：DM    2026-10-05</t>
         </is>
       </c>
     </row>
